--- a/_presentations/Draft budget _ Mobilité .xlsx
+++ b/_presentations/Draft budget _ Mobilité .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xt/github/meaps/_presentations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1ECD95FE-A348-9D4A-BCC9-FA889F8A382E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00562A8B-CA71-8940-B586-F76AD04E5B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19180" yWindow="4020" windowWidth="31620" windowHeight="24380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-43480" yWindow="-4660" windowWidth="34140" windowHeight="26900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Axe de recherche" sheetId="1" r:id="rId1"/>
@@ -4118,7 +4118,8 @@
   <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.5" customWidth="1"/>
     <col min="12" max="12" width="16.83203125" customWidth="1"/>
   </cols>
